--- a/backend/nasa_dados.xlsx
+++ b/backend/nasa_dados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,16 +479,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>andre victor cirino alves</t>
+          <t>andre</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>andre.victor2187@gmail.com</t>
+          <t>andre.victoe3434@gmail.com</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
         <v>50</v>
@@ -503,94 +503,12 @@
         <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J2" t="n">
-        <v>49.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>Carga moderada</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>andre</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>andre.victor2187@gmail.com</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J3" t="n">
-        <v>50</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Carga moderada</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">andre </t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>andre.victor2187@gmail.com</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K4" t="inlineStr">
         <is>
           <t>Carga moderada</t>
         </is>
